--- a/data/trans_orig/Q64C-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q64C-Provincia-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de horas que trabaja a la semana</t>
+          <t>Número medio de horas que trabaja a la semana (tasa de respuesta: 97,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,45; 43,33</t>
+          <t>40,52; 43,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42,98; 47,72</t>
+          <t>42,85; 47,78</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,59; 44,22</t>
+          <t>39,79; 44,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,35; 39,56</t>
+          <t>37,19; 39,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,96; 40,98</t>
+          <t>36,84; 41,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,74; 40,98</t>
+          <t>34,54; 41,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,34; 39,81</t>
+          <t>34,68; 39,98</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,78; 38,36</t>
+          <t>36,74; 38,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,54; 41,93</t>
+          <t>39,54; 42,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40,19; 44,33</t>
+          <t>40,14; 44,42</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38,18; 41,64</t>
+          <t>38,35; 41,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,41; 38,83</t>
+          <t>37,35; 38,88</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,93; 41,75</t>
+          <t>38,92; 41,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,86; 40,87</t>
+          <t>37,92; 41,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,57; 39,79</t>
+          <t>36,81; 39,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39,71; 41,91</t>
+          <t>39,76; 41,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,66; 37,66</t>
+          <t>32,42; 37,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,85; 37,82</t>
+          <t>32,85; 37,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,79; 37,58</t>
+          <t>32,72; 37,54</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,23; 37,24</t>
+          <t>34,24; 37,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,03; 39,62</t>
+          <t>37,24; 39,77</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,4; 39,19</t>
+          <t>36,53; 39,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35,62; 38,48</t>
+          <t>35,72; 38,42</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,79; 39,69</t>
+          <t>37,81; 39,74</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,42; 43,65</t>
+          <t>41,31; 43,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41,13; 43,7</t>
+          <t>41,12; 43,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,45; 39,12</t>
+          <t>36,38; 39,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39,21; 42,61</t>
+          <t>39,31; 42,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,43; 38,18</t>
+          <t>34,31; 38,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,67; 37,04</t>
+          <t>32,53; 36,83</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,07; 36,13</t>
+          <t>32,16; 36,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,89; 37,75</t>
+          <t>34,72; 37,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,15; 41,33</t>
+          <t>39,29; 41,34</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38,43; 40,85</t>
+          <t>38,41; 40,72</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,26; 37,52</t>
+          <t>35,13; 37,62</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,81; 40,13</t>
+          <t>37,77; 40,21</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,73; 42,06</t>
+          <t>39,81; 41,97</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,08; 42,58</t>
+          <t>39,18; 42,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,78; 44,54</t>
+          <t>39,58; 44,34</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38,24; 42,72</t>
+          <t>38,29; 42,75</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>35,1; 38,92</t>
+          <t>34,99; 38,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,16; 33,67</t>
+          <t>29,41; 33,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,21; 31,22</t>
+          <t>25,27; 31,17</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,42; 35,97</t>
+          <t>24,5; 36,19</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,49; 40,46</t>
+          <t>38,43; 40,39</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35,58; 38,44</t>
+          <t>35,59; 38,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>33,96; 38,28</t>
+          <t>34,23; 38,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,67; 38,06</t>
+          <t>27,44; 38,2</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,28; 43,54</t>
+          <t>40,27; 43,4</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38,12; 42,02</t>
+          <t>38,38; 42,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,46; 42,87</t>
+          <t>39,44; 42,99</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39,68; 41,26</t>
+          <t>39,64; 41,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,37; 39,39</t>
+          <t>34,64; 39,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,42; 37,03</t>
+          <t>31,26; 36,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,68; 42,68</t>
+          <t>36,41; 42,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>39,28; 40,43</t>
+          <t>39,31; 40,43</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39,04; 41,62</t>
+          <t>39,03; 41,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36,11; 39,35</t>
+          <t>35,93; 39,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38,86; 42,18</t>
+          <t>38,83; 42,22</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>39,68; 40,75</t>
+          <t>39,72; 40,65</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40,79; 43,56</t>
+          <t>40,88; 43,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40,83; 45,04</t>
+          <t>40,72; 45,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41,5; 44,43</t>
+          <t>41,28; 44,33</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40,12; 42,17</t>
+          <t>40,09; 42,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36,27; 41,58</t>
+          <t>36,69; 42,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,37; 38,59</t>
+          <t>31,29; 38,07</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,81; 41,81</t>
+          <t>37,74; 41,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34,76; 37,92</t>
+          <t>34,65; 37,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39,85; 42,38</t>
+          <t>39,78; 42,32</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38,24; 41,92</t>
+          <t>38,33; 41,99</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40,35; 42,95</t>
+          <t>40,4; 42,86</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>38,38; 40,14</t>
+          <t>38,29; 40,12</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>38,59; 41,27</t>
+          <t>38,6; 41,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40,27; 42,51</t>
+          <t>40,19; 42,45</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35,93; 38,65</t>
+          <t>35,94; 38,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37,73; 39,81</t>
+          <t>37,8; 39,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,39; 39,67</t>
+          <t>35,2; 39,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,87; 39,86</t>
+          <t>36,83; 39,86</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,07; 33,88</t>
+          <t>31,2; 34,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>32,82; 34,95</t>
+          <t>32,82; 34,9</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>37,88; 40,26</t>
+          <t>37,9; 40,22</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39,3; 41,03</t>
+          <t>39,26; 41,09</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34,28; 36,25</t>
+          <t>34,28; 36,28</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35,75; 37,24</t>
+          <t>35,72; 37,26</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>40,28; 42,25</t>
+          <t>40,38; 42,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>39,4; 41,06</t>
+          <t>39,38; 40,98</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38,32; 40,25</t>
+          <t>38,53; 40,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,97; 39,31</t>
+          <t>14,42; 39,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>36,04; 38,91</t>
+          <t>36,02; 38,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,82; 37,52</t>
+          <t>34,85; 37,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,14; 37,99</t>
+          <t>35,15; 37,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,59; 35,46</t>
+          <t>32,63; 35,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>39,24; 40,82</t>
+          <t>39,18; 40,82</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37,76; 39,25</t>
+          <t>37,68; 39,22</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37,26; 38,97</t>
+          <t>37,42; 39,06</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,87; 37,3</t>
+          <t>17,92; 37,3</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40,69; 41,6</t>
+          <t>40,71; 41,65</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>40,71; 41,75</t>
+          <t>40,76; 41,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38,84; 40,02</t>
+          <t>38,88; 40,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25,93; 39,89</t>
+          <t>25,59; 39,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>36,34; 37,83</t>
+          <t>36,41; 37,96</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,07; 36,69</t>
+          <t>35,06; 36,56</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,16; 35,67</t>
+          <t>34,18; 35,67</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>32,49; 35,82</t>
+          <t>32,33; 35,79</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>39,36; 40,13</t>
+          <t>39,34; 40,16</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>38,67; 39,51</t>
+          <t>38,59; 39,51</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>36,99; 37,96</t>
+          <t>37,06; 38,02</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>28,16; 37,84</t>
+          <t>28,34; 37,75</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q64C-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/Q64C-Provincia-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38,68</t>
+          <t>39,41</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>37,61</t>
+          <t>37,65</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>38,23</t>
+          <t>38,65</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>40,52; 43,36</t>
+          <t>40,29; 43,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42,85; 47,78</t>
+          <t>42,8; 48,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>39,79; 44,49</t>
+          <t>39,74; 44,29</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>37,19; 39,68</t>
+          <t>38,24; 40,21</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>36,84; 41,37</t>
+          <t>36,85; 41,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,54; 41,42</t>
+          <t>34,48; 41,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,68; 39,98</t>
+          <t>34,72; 40,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>36,74; 38,35</t>
+          <t>36,68; 38,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,54; 42,03</t>
+          <t>39,56; 42,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>40,14; 44,42</t>
+          <t>40,25; 44,26</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38,35; 41,77</t>
+          <t>38,3; 41,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>37,35; 38,88</t>
+          <t>38,0; 39,29</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40,86</t>
+          <t>40,98</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>35,68</t>
+          <t>35,75</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38,74</t>
+          <t>38,83</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>38,92; 41,71</t>
+          <t>38,81; 41,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>37,92; 41,09</t>
+          <t>37,91; 41,05</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,81; 39,85</t>
+          <t>36,68; 39,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>39,76; 41,94</t>
+          <t>39,96; 42,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,42; 37,52</t>
+          <t>32,43; 37,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,85; 37,54</t>
+          <t>33,13; 37,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,72; 37,54</t>
+          <t>32,37; 37,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>34,24; 37,23</t>
+          <t>34,24; 37,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>37,24; 39,77</t>
+          <t>37,2; 39,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36,53; 39,16</t>
+          <t>36,53; 39,17</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35,72; 38,42</t>
+          <t>35,75; 38,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,81; 39,74</t>
+          <t>38,01; 39,75</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41,09</t>
+          <t>41,04</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>36,42</t>
+          <t>36,14</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>39,0</t>
+          <t>38,83</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>41,31; 43,73</t>
+          <t>41,34; 43,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>41,12; 43,56</t>
+          <t>41,13; 43,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>36,38; 39,06</t>
+          <t>36,37; 39,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>39,31; 42,66</t>
+          <t>39,08; 42,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,31; 38,18</t>
+          <t>34,36; 37,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,53; 36,83</t>
+          <t>32,67; 37,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>32,16; 36,05</t>
+          <t>32,08; 36,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,72; 37,63</t>
+          <t>34,46; 37,36</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>39,29; 41,34</t>
+          <t>39,3; 41,36</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38,41; 40,72</t>
+          <t>38,39; 40,89</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>35,13; 37,62</t>
+          <t>35,09; 37,56</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>37,77; 40,21</t>
+          <t>37,62; 40,04</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>40,26</t>
+          <t>41,16</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1103,7 +1103,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>30,85</t>
+          <t>33,85</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>34,43</t>
+          <t>37,76</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>39,81; 41,97</t>
+          <t>39,74; 41,99</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,18; 42,62</t>
+          <t>39,17; 42,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>39,58; 44,34</t>
+          <t>39,4; 44,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>38,29; 42,75</t>
+          <t>39,07; 43,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>34,99; 38,81</t>
+          <t>35,27; 39,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,41; 33,95</t>
+          <t>29,29; 33,94</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,27; 31,17</t>
+          <t>25,3; 31,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24,5; 36,19</t>
+          <t>32,09; 35,29</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>38,43; 40,39</t>
+          <t>38,3; 40,47</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35,59; 38,86</t>
+          <t>35,63; 38,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>34,23; 38,28</t>
+          <t>34,04; 38,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>27,44; 38,2</t>
+          <t>36,31; 39,46</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>40,53</t>
+          <t>40,8</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>39,88</t>
+          <t>39,98</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40,21</t>
+          <t>40,4</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>40,27; 43,4</t>
+          <t>40,15; 43,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38,38; 42,02</t>
+          <t>38,02; 41,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>39,44; 42,99</t>
+          <t>39,34; 43,18</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39,64; 41,23</t>
+          <t>39,92; 41,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,64; 39,38</t>
+          <t>34,55; 39,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,26; 36,89</t>
+          <t>30,96; 36,98</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,41; 42,5</t>
+          <t>36,72; 42,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>39,31; 40,43</t>
+          <t>39,34; 40,52</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>39,03; 41,8</t>
+          <t>39,06; 41,78</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35,93; 39,29</t>
+          <t>35,95; 39,4</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38,83; 42,22</t>
+          <t>38,85; 42,2</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>39,72; 40,65</t>
+          <t>39,88; 40,88</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>41,11</t>
+          <t>41,05</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>36,57</t>
+          <t>36,5</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>39,33</t>
+          <t>39,27</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1416,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>40,88; 43,58</t>
+          <t>40,93; 43,69</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>40,72; 45,03</t>
+          <t>40,76; 44,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41,28; 44,33</t>
+          <t>41,3; 44,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40,09; 42,11</t>
+          <t>40,03; 41,97</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36,69; 42,19</t>
+          <t>36,54; 42,03</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>31,29; 38,07</t>
+          <t>30,87; 37,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>37,74; 41,78</t>
+          <t>37,9; 41,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>34,65; 37,9</t>
+          <t>34,82; 37,74</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>39,78; 42,32</t>
+          <t>39,8; 42,3</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>38,33; 41,99</t>
+          <t>38,16; 41,87</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40,4; 42,86</t>
+          <t>40,36; 42,83</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>38,29; 40,12</t>
+          <t>38,34; 40,08</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38,86</t>
+          <t>38,55</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>33,93</t>
+          <t>33,77</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>36,5</t>
+          <t>36,23</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>38,6; 41,32</t>
+          <t>38,54; 41,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40,19; 42,45</t>
+          <t>40,21; 42,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>35,94; 38,72</t>
+          <t>35,97; 38,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37,8; 39,82</t>
+          <t>37,35; 39,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>35,2; 39,67</t>
+          <t>35,2; 39,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,83; 39,86</t>
+          <t>36,87; 39,99</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>31,2; 34,01</t>
+          <t>31,12; 34,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>32,82; 34,9</t>
+          <t>32,67; 34,79</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>37,9; 40,22</t>
+          <t>37,97; 40,15</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39,26; 41,09</t>
+          <t>39,3; 41,04</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34,28; 36,28</t>
+          <t>34,21; 36,2</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>35,72; 37,26</t>
+          <t>35,46; 36,9</t>
         </is>
       </c>
     </row>
@@ -1643,7 +1643,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26,84</t>
+          <t>39,06</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>34,31</t>
+          <t>34,75</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>29,09</t>
+          <t>37,31</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1696,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>40,38; 42,22</t>
+          <t>40,3; 42,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>39,38; 40,98</t>
+          <t>39,34; 40,95</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38,53; 40,34</t>
+          <t>38,43; 40,37</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14,42; 39,18</t>
+          <t>38,1; 39,97</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>36,02; 38,95</t>
+          <t>36,04; 38,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,85; 37,54</t>
+          <t>34,84; 37,44</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>35,15; 37,94</t>
+          <t>35,1; 37,87</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>32,63; 35,46</t>
+          <t>33,57; 35,75</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>39,18; 40,82</t>
+          <t>39,24; 40,86</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>37,68; 39,22</t>
+          <t>37,67; 39,22</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37,42; 39,06</t>
+          <t>37,38; 38,93</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>17,92; 37,3</t>
+          <t>36,5; 38,03</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1783,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35,7</t>
+          <t>39,86</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>34,87</t>
+          <t>35,47</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1823,7 +1823,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>35,35</t>
+          <t>37,92</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1836,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>40,71; 41,65</t>
+          <t>40,67; 41,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>40,76; 41,78</t>
+          <t>40,77; 41,83</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>38,88; 40,07</t>
+          <t>38,87; 40,08</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>25,59; 39,87</t>
+          <t>39,41; 40,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>36,41; 37,96</t>
+          <t>36,34; 37,94</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35,06; 36,56</t>
+          <t>35,09; 36,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,18; 35,67</t>
+          <t>34,11; 35,66</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>32,33; 35,79</t>
+          <t>34,96; 35,93</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>39,34; 40,16</t>
+          <t>39,34; 40,18</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>38,59; 39,51</t>
+          <t>38,6; 39,51</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>37,06; 38,02</t>
+          <t>37,05; 38,01</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>28,34; 37,75</t>
+          <t>37,6; 38,23</t>
         </is>
       </c>
     </row>
